--- a/pastoral-projects/tutor-time-takeover/downloads/Tutor_Time_Takeover_Tracker.xlsx
+++ b/pastoral-projects/tutor-time-takeover/downloads/Tutor_Time_Takeover_Tracker.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="ddd d mmmm"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,83 +31,163 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Karla"/>
+      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="005C6552"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Libre Caslon Display"/>
+      <name val="Georgia"/>
       <b val="1"/>
       <color rgb="00854274"/>
       <sz val="20"/>
     </font>
     <font>
-      <name val="Karla"/>
+      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="005C6552"/>
       <sz val="10.5"/>
     </font>
     <font>
-      <name val="Karla"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00854274"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Karla"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="002E4436"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Karla"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00854274"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Karla"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="002E4436"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Karla"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Karla"/>
+      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="007A6E7A"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Karla"/>
+      <name val="Calibri"/>
       <color rgb="000000CC"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Karla"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Karla"/>
+      <name val="Calibri"/>
       <color rgb="002E4436"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Libre Caslon Display"/>
+      <name val="Georgia"/>
       <b val="1"/>
       <color rgb="00854274"/>
       <sz val="13"/>
     </font>
     <font>
-      <name val="Karla"/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002E4436"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="005C6552"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <color rgb="00854274"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="005C6552"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00854274"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002E4436"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00854274"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002E4436"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="007A6E7A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000000CC"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="002E4436"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <color rgb="00854274"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="002E4436"/>
       <sz val="11"/>
@@ -141,7 +221,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -226,11 +306,60 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="00854274"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D5C3D1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00854274"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D5C3D1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D5C3D1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D5C3D1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D5C3D1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -285,6 +414,61 @@
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -430,6 +614,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -460,6 +647,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -756,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G46"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -768,435 +958,440 @@
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="16" customHeight="1">
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="24" t="inlineStr">
         <is>
           <t>The Pastoral Guide</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t>Tutor Time Takeover: sign-up sheet</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Your tutor puts in the dates. To sign up, pick a free date and fill in your name, your topic, how long it will be and what you need. Your tutor marks Topic approved once you have talked it through.</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
+      <c r="C5" s="27" t="n"/>
+      <c r="D5" s="27" t="n"/>
+      <c r="E5" s="27" t="n"/>
+      <c r="F5" s="27" t="n"/>
+      <c r="G5" s="28" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-    </row>
+      <c r="B6" s="29" t="n"/>
+      <c r="C6" s="30" t="n"/>
+      <c r="D6" s="30" t="n"/>
+      <c r="E6" s="30" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="31" t="n"/>
+    </row>
+    <row r="7"/>
     <row r="8" ht="21" customHeight="1">
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>Dates set</t>
         </is>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="33">
         <f>COUNT(B14:B43)</f>
         <v/>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="32" t="inlineStr">
         <is>
           <t>Taken</t>
         </is>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="33">
         <f>SUMPRODUCT((B14:B43&lt;&gt;"")*(C14:C43&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1">
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Still free</t>
         </is>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="33">
         <f>C8-E8</f>
         <v/>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="32" t="inlineStr">
         <is>
           <t>Waiting for a yes</t>
         </is>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="33">
         <f>SUMPRODUCT((C14:C43&lt;&gt;"")*(G14:G43&lt;&gt;"Yes"))</f>
         <v/>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>Your tutor</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="35" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="35" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="35" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="35" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="34" t="inlineStr">
         <is>
           <t>Your tutor</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve"> Date</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve"> Name</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve"> Topic</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve"> How long</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve"> What I need</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve"> Topic approved</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve"> For example: Fri 2 October</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sam</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve"> How to solve a Rubik’s cube in under two minutes</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve"> 30 minutes</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve"> The projector, and six cubes to pass round</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve"> Yes</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="13" t="n"/>
+      <c r="B14" s="38" t="n"/>
+      <c r="C14" s="39" t="n"/>
+      <c r="D14" s="39" t="n"/>
+      <c r="E14" s="39" t="n"/>
+      <c r="F14" s="39" t="n"/>
+      <c r="G14" s="39" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="13" t="n"/>
-      <c r="D15" s="13" t="n"/>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="13" t="n"/>
-      <c r="G15" s="13" t="n"/>
+      <c r="B15" s="38" t="n"/>
+      <c r="C15" s="39" t="n"/>
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="39" t="n"/>
+      <c r="F15" s="39" t="n"/>
+      <c r="G15" s="39" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="13" t="n"/>
+      <c r="B16" s="38" t="n"/>
+      <c r="C16" s="39" t="n"/>
+      <c r="D16" s="39" t="n"/>
+      <c r="E16" s="39" t="n"/>
+      <c r="F16" s="39" t="n"/>
+      <c r="G16" s="39" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="13" t="n"/>
+      <c r="B17" s="38" t="n"/>
+      <c r="C17" s="39" t="n"/>
+      <c r="D17" s="39" t="n"/>
+      <c r="E17" s="39" t="n"/>
+      <c r="F17" s="39" t="n"/>
+      <c r="G17" s="39" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="13" t="n"/>
+      <c r="B18" s="38" t="n"/>
+      <c r="C18" s="39" t="n"/>
+      <c r="D18" s="39" t="n"/>
+      <c r="E18" s="39" t="n"/>
+      <c r="F18" s="39" t="n"/>
+      <c r="G18" s="39" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="13" t="n"/>
+      <c r="B19" s="38" t="n"/>
+      <c r="C19" s="39" t="n"/>
+      <c r="D19" s="39" t="n"/>
+      <c r="E19" s="39" t="n"/>
+      <c r="F19" s="39" t="n"/>
+      <c r="G19" s="39" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="13" t="n"/>
+      <c r="B20" s="38" t="n"/>
+      <c r="C20" s="39" t="n"/>
+      <c r="D20" s="39" t="n"/>
+      <c r="E20" s="39" t="n"/>
+      <c r="F20" s="39" t="n"/>
+      <c r="G20" s="39" t="n"/>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="13" t="n"/>
+      <c r="B21" s="38" t="n"/>
+      <c r="C21" s="39" t="n"/>
+      <c r="D21" s="39" t="n"/>
+      <c r="E21" s="39" t="n"/>
+      <c r="F21" s="39" t="n"/>
+      <c r="G21" s="39" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="13" t="n"/>
+      <c r="B22" s="38" t="n"/>
+      <c r="C22" s="39" t="n"/>
+      <c r="D22" s="39" t="n"/>
+      <c r="E22" s="39" t="n"/>
+      <c r="F22" s="39" t="n"/>
+      <c r="G22" s="39" t="n"/>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="13" t="n"/>
+      <c r="B23" s="38" t="n"/>
+      <c r="C23" s="39" t="n"/>
+      <c r="D23" s="39" t="n"/>
+      <c r="E23" s="39" t="n"/>
+      <c r="F23" s="39" t="n"/>
+      <c r="G23" s="39" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="13" t="n"/>
+      <c r="B24" s="38" t="n"/>
+      <c r="C24" s="39" t="n"/>
+      <c r="D24" s="39" t="n"/>
+      <c r="E24" s="39" t="n"/>
+      <c r="F24" s="39" t="n"/>
+      <c r="G24" s="39" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="13" t="n"/>
-      <c r="D25" s="13" t="n"/>
-      <c r="E25" s="13" t="n"/>
-      <c r="F25" s="13" t="n"/>
-      <c r="G25" s="13" t="n"/>
+      <c r="B25" s="38" t="n"/>
+      <c r="C25" s="39" t="n"/>
+      <c r="D25" s="39" t="n"/>
+      <c r="E25" s="39" t="n"/>
+      <c r="F25" s="39" t="n"/>
+      <c r="G25" s="39" t="n"/>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="13" t="n"/>
+      <c r="B26" s="38" t="n"/>
+      <c r="C26" s="39" t="n"/>
+      <c r="D26" s="39" t="n"/>
+      <c r="E26" s="39" t="n"/>
+      <c r="F26" s="39" t="n"/>
+      <c r="G26" s="39" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="13" t="n"/>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="13" t="n"/>
-      <c r="G27" s="13" t="n"/>
+      <c r="B27" s="38" t="n"/>
+      <c r="C27" s="39" t="n"/>
+      <c r="D27" s="39" t="n"/>
+      <c r="E27" s="39" t="n"/>
+      <c r="F27" s="39" t="n"/>
+      <c r="G27" s="39" t="n"/>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="13" t="n"/>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="13" t="n"/>
+      <c r="B28" s="38" t="n"/>
+      <c r="C28" s="39" t="n"/>
+      <c r="D28" s="39" t="n"/>
+      <c r="E28" s="39" t="n"/>
+      <c r="F28" s="39" t="n"/>
+      <c r="G28" s="39" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="13" t="n"/>
+      <c r="B29" s="38" t="n"/>
+      <c r="C29" s="39" t="n"/>
+      <c r="D29" s="39" t="n"/>
+      <c r="E29" s="39" t="n"/>
+      <c r="F29" s="39" t="n"/>
+      <c r="G29" s="39" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="B30" s="12" t="n"/>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="13" t="n"/>
+      <c r="B30" s="38" t="n"/>
+      <c r="C30" s="39" t="n"/>
+      <c r="D30" s="39" t="n"/>
+      <c r="E30" s="39" t="n"/>
+      <c r="F30" s="39" t="n"/>
+      <c r="G30" s="39" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="13" t="n"/>
-      <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
-      <c r="G31" s="13" t="n"/>
+      <c r="B31" s="38" t="n"/>
+      <c r="C31" s="39" t="n"/>
+      <c r="D31" s="39" t="n"/>
+      <c r="E31" s="39" t="n"/>
+      <c r="F31" s="39" t="n"/>
+      <c r="G31" s="39" t="n"/>
     </row>
     <row r="32" ht="24" customHeight="1">
-      <c r="B32" s="12" t="n"/>
-      <c r="C32" s="13" t="n"/>
-      <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="13" t="n"/>
+      <c r="B32" s="38" t="n"/>
+      <c r="C32" s="39" t="n"/>
+      <c r="D32" s="39" t="n"/>
+      <c r="E32" s="39" t="n"/>
+      <c r="F32" s="39" t="n"/>
+      <c r="G32" s="39" t="n"/>
     </row>
     <row r="33" ht="24" customHeight="1">
-      <c r="B33" s="12" t="n"/>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="13" t="n"/>
+      <c r="B33" s="38" t="n"/>
+      <c r="C33" s="39" t="n"/>
+      <c r="D33" s="39" t="n"/>
+      <c r="E33" s="39" t="n"/>
+      <c r="F33" s="39" t="n"/>
+      <c r="G33" s="39" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="B34" s="12" t="n"/>
-      <c r="C34" s="13" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="13" t="n"/>
+      <c r="B34" s="38" t="n"/>
+      <c r="C34" s="39" t="n"/>
+      <c r="D34" s="39" t="n"/>
+      <c r="E34" s="39" t="n"/>
+      <c r="F34" s="39" t="n"/>
+      <c r="G34" s="39" t="n"/>
     </row>
     <row r="35" ht="24" customHeight="1">
-      <c r="B35" s="12" t="n"/>
-      <c r="C35" s="13" t="n"/>
-      <c r="D35" s="13" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="13" t="n"/>
+      <c r="B35" s="38" t="n"/>
+      <c r="C35" s="39" t="n"/>
+      <c r="D35" s="39" t="n"/>
+      <c r="E35" s="39" t="n"/>
+      <c r="F35" s="39" t="n"/>
+      <c r="G35" s="39" t="n"/>
     </row>
     <row r="36" ht="24" customHeight="1">
-      <c r="B36" s="12" t="n"/>
-      <c r="C36" s="13" t="n"/>
-      <c r="D36" s="13" t="n"/>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="13" t="n"/>
+      <c r="B36" s="38" t="n"/>
+      <c r="C36" s="39" t="n"/>
+      <c r="D36" s="39" t="n"/>
+      <c r="E36" s="39" t="n"/>
+      <c r="F36" s="39" t="n"/>
+      <c r="G36" s="39" t="n"/>
     </row>
     <row r="37" ht="24" customHeight="1">
-      <c r="B37" s="12" t="n"/>
-      <c r="C37" s="13" t="n"/>
-      <c r="D37" s="13" t="n"/>
-      <c r="E37" s="13" t="n"/>
-      <c r="F37" s="13" t="n"/>
-      <c r="G37" s="13" t="n"/>
+      <c r="B37" s="38" t="n"/>
+      <c r="C37" s="39" t="n"/>
+      <c r="D37" s="39" t="n"/>
+      <c r="E37" s="39" t="n"/>
+      <c r="F37" s="39" t="n"/>
+      <c r="G37" s="39" t="n"/>
     </row>
     <row r="38" ht="24" customHeight="1">
-      <c r="B38" s="12" t="n"/>
-      <c r="C38" s="13" t="n"/>
-      <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
-      <c r="G38" s="13" t="n"/>
+      <c r="B38" s="38" t="n"/>
+      <c r="C38" s="39" t="n"/>
+      <c r="D38" s="39" t="n"/>
+      <c r="E38" s="39" t="n"/>
+      <c r="F38" s="39" t="n"/>
+      <c r="G38" s="39" t="n"/>
     </row>
     <row r="39" ht="24" customHeight="1">
-      <c r="B39" s="12" t="n"/>
-      <c r="C39" s="13" t="n"/>
-      <c r="D39" s="13" t="n"/>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="n"/>
-      <c r="G39" s="13" t="n"/>
+      <c r="B39" s="38" t="n"/>
+      <c r="C39" s="39" t="n"/>
+      <c r="D39" s="39" t="n"/>
+      <c r="E39" s="39" t="n"/>
+      <c r="F39" s="39" t="n"/>
+      <c r="G39" s="39" t="n"/>
     </row>
     <row r="40" ht="24" customHeight="1">
-      <c r="B40" s="12" t="n"/>
-      <c r="C40" s="13" t="n"/>
-      <c r="D40" s="13" t="n"/>
-      <c r="E40" s="13" t="n"/>
-      <c r="F40" s="13" t="n"/>
-      <c r="G40" s="13" t="n"/>
+      <c r="B40" s="38" t="n"/>
+      <c r="C40" s="39" t="n"/>
+      <c r="D40" s="39" t="n"/>
+      <c r="E40" s="39" t="n"/>
+      <c r="F40" s="39" t="n"/>
+      <c r="G40" s="39" t="n"/>
     </row>
     <row r="41" ht="24" customHeight="1">
-      <c r="B41" s="12" t="n"/>
-      <c r="C41" s="13" t="n"/>
-      <c r="D41" s="13" t="n"/>
-      <c r="E41" s="13" t="n"/>
-      <c r="F41" s="13" t="n"/>
-      <c r="G41" s="13" t="n"/>
+      <c r="B41" s="38" t="n"/>
+      <c r="C41" s="39" t="n"/>
+      <c r="D41" s="39" t="n"/>
+      <c r="E41" s="39" t="n"/>
+      <c r="F41" s="39" t="n"/>
+      <c r="G41" s="39" t="n"/>
     </row>
     <row r="42" ht="24" customHeight="1">
-      <c r="B42" s="12" t="n"/>
-      <c r="C42" s="13" t="n"/>
-      <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
-      <c r="G42" s="13" t="n"/>
+      <c r="B42" s="38" t="n"/>
+      <c r="C42" s="39" t="n"/>
+      <c r="D42" s="39" t="n"/>
+      <c r="E42" s="39" t="n"/>
+      <c r="F42" s="39" t="n"/>
+      <c r="G42" s="39" t="n"/>
     </row>
     <row r="43" ht="24" customHeight="1">
-      <c r="B43" s="12" t="n"/>
-      <c r="C43" s="13" t="n"/>
-      <c r="D43" s="13" t="n"/>
-      <c r="E43" s="13" t="n"/>
-      <c r="F43" s="13" t="n"/>
-      <c r="G43" s="13" t="n"/>
-    </row>
+      <c r="B43" s="38" t="n"/>
+      <c r="C43" s="39" t="n"/>
+      <c r="D43" s="39" t="n"/>
+      <c r="E43" s="39" t="n"/>
+      <c r="F43" s="39" t="n"/>
+      <c r="G43" s="39" t="n"/>
+    </row>
+    <row r="44"/>
     <row r="45" ht="18" customHeight="1">
-      <c r="B45" s="14" t="inlineStr">
+      <c r="B45" s="40" t="inlineStr">
         <is>
           <t>Pale yellow cells are for typing into. A free date shows pale pink across the row, Topic approved turns amber until your tutor says yes and green once they have, and a date that has passed goes grey. Need more rows? Copy the last one and paste it underneath.</t>
         </is>
       </c>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="n"/>
-      <c r="G45" s="4" t="n"/>
+      <c r="C45" s="27" t="n"/>
+      <c r="D45" s="27" t="n"/>
+      <c r="E45" s="27" t="n"/>
+      <c r="F45" s="27" t="n"/>
+      <c r="G45" s="28" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="B46" s="5" t="n"/>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="n"/>
-      <c r="G46" s="4" t="n"/>
+      <c r="B46" s="29" t="n"/>
+      <c r="C46" s="30" t="n"/>
+      <c r="D46" s="30" t="n"/>
+      <c r="E46" s="30" t="n"/>
+      <c r="F46" s="30" t="n"/>
+      <c r="G46" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1252,7 +1447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -1264,87 +1459,92 @@
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="16" customHeight="1">
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="24" t="inlineStr">
         <is>
           <t>The Pastoral Guide</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t>Setting up the sign-up sheet</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="62" customHeight="1">
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="42" t="inlineStr">
         <is>
           <t>Type your dates into the Date column on the first tab, one date to a row, and leave the rest of each row empty. Once a month or once a half term works well.</t>
         </is>
       </c>
-      <c r="D5" s="17" t="n"/>
-      <c r="E5" s="17" t="n"/>
-      <c r="F5" s="17" t="n"/>
-      <c r="G5" s="17" t="n"/>
-    </row>
+      <c r="D5" s="30" t="n"/>
+      <c r="E5" s="30" t="n"/>
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="30" t="n"/>
+    </row>
+    <row r="6"/>
     <row r="7" ht="62" customHeight="1">
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="42" t="inlineStr">
         <is>
           <t>Share it with the form. For Google Classroom, upload it to Google Drive, open it and choose File, then Save as Google Sheets. Attach that copy to a Classroom post and choose “Students can edit file”. For Microsoft Teams, upload it to the Files tab of a class channel, not to Class Materials, which students cannot edit.</t>
         </is>
       </c>
-      <c r="D7" s="17" t="n"/>
-      <c r="E7" s="17" t="n"/>
-      <c r="F7" s="17" t="n"/>
-      <c r="G7" s="17" t="n"/>
-    </row>
+      <c r="D7" s="30" t="n"/>
+      <c r="E7" s="30" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
+    </row>
+    <row r="8"/>
     <row r="9" ht="62" customHeight="1">
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="41" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="42" t="inlineStr">
         <is>
           <t>When somebody signs up, talk the topic through with them and set Topic approved to Yes. The counts at the top tell you how many dates are left and how many are still waiting for you.</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n"/>
-      <c r="E9" s="17" t="n"/>
-      <c r="F9" s="17" t="n"/>
-      <c r="G9" s="17" t="n"/>
-    </row>
+      <c r="D9" s="30" t="n"/>
+      <c r="E9" s="30" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
+    </row>
+    <row r="10"/>
     <row r="11" ht="24" customHeight="1">
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="43" t="inlineStr">
         <is>
           <t>How long, by year group</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve"> Year group</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve"> How long</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve"> What fits in it</t>
         </is>
@@ -1354,84 +1554,84 @@
       <c r="G12" s="20" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="44" t="inlineStr">
         <is>
           <t>Year 7</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="45" t="inlineStr">
         <is>
           <t>20 minutes</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="46" t="inlineStr">
         <is>
           <t>A short introduction, a little background and one activity. Hands-on works best.</t>
         </is>
       </c>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="19" t="n"/>
+      <c r="G13" s="20" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="44" t="inlineStr">
         <is>
           <t>Year 8 and 9</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="45" t="inlineStr">
         <is>
           <t>20 to 30 minutes</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="46" t="inlineStr">
         <is>
           <t>Room for two activities, or one longer one. A quiz goes down well.</t>
         </is>
       </c>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="20" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="44" t="inlineStr">
         <is>
           <t>Year 10 and 11</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="45" t="inlineStr">
         <is>
           <t>30 to 45 minutes</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="46" t="inlineStr">
         <is>
           <t>The background can go deeper, and one activity can be in pairs or groups.</t>
         </is>
       </c>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="19" t="n"/>
+      <c r="G15" s="20" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="44" t="inlineStr">
         <is>
           <t>Sixth form</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="45" t="inlineStr">
         <is>
           <t>30 minutes to an hour</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="46" t="inlineStr">
         <is>
           <t>A full lesson if your slot allows, with proper time for questions.</t>
         </is>
       </c>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="19" t="n"/>
+      <c r="G16" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
